--- a/words.xlsx
+++ b/words.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5A3B9F-809A-4870-986E-68DB90DE04ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53841FE-9F71-4B4D-A273-97AF9C6492E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="570" yWindow="0" windowWidth="11355" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="単語" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>番号</t>
     <rPh sb="0" eb="2">
@@ -81,6 +81,40 @@
     <t>同封する</t>
     <rPh sb="0" eb="2">
       <t>ドウフウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>stagnant</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>adj</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>停滞した</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>alertness</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機敏さ</t>
+    <rPh sb="0" eb="2">
+      <t>キビン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>clarify</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>明確にする</t>
+    <rPh sb="0" eb="2">
+      <t>メイカク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -459,21 +493,48 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" t="str">
+      <c r="A4">
         <f>IF(B4&lt;&gt;"",COUNTA($B$2:B4),"")</f>
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" t="str">
+      <c r="A5">
         <f>IF(B5&lt;&gt;"",COUNTA($B$2:B5),"")</f>
-        <v/>
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" t="str">
+      <c r="A6">
         <f>IF(B6&lt;&gt;"",COUNTA($B$2:B6),"")</f>
-        <v/>
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4">

--- a/words.xlsx
+++ b/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53841FE-9F71-4B4D-A273-97AF9C6492E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D36521-E45A-4B20-AA39-796C46CD957D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="495" yWindow="2535" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="単語" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>番号</t>
     <rPh sb="0" eb="2">
@@ -116,6 +116,14 @@
     <rPh sb="0" eb="2">
       <t>メイカク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pertain</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>関係する</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -538,9 +546,18 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" t="str">
+      <c r="A7">
         <f>IF(B7&lt;&gt;"",COUNTA($B$2:B7),"")</f>
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:4">

--- a/words.xlsx
+++ b/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D36521-E45A-4B20-AA39-796C46CD957D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0C3DC7-83EF-43FC-BB4A-3873CD7E958F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="495" yWindow="2535" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1155" yWindow="2940" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="単語" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>番号</t>
     <rPh sb="0" eb="2">
@@ -124,6 +124,17 @@
   </si>
   <si>
     <t>関係する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>attain</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>達成する</t>
+    <rPh sb="0" eb="2">
+      <t>タッセイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -561,9 +572,18 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" t="str">
+      <c r="A8">
         <f>IF(B8&lt;&gt;"",COUNTA($B$2:B8),"")</f>
-        <v/>
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:4">

--- a/words.xlsx
+++ b/words.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0C3DC7-83EF-43FC-BB4A-3873CD7E958F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8001E1-8BB4-438D-A063-CA3BA2112008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1155" yWindow="2940" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5025" yWindow="2430" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="単語" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
   <si>
     <t>番号</t>
     <rPh sb="0" eb="2">
@@ -135,6 +135,14 @@
     <rPh sb="0" eb="2">
       <t>タッセイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>conformity</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>適合性</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -587,9 +595,18 @@
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" t="str">
+      <c r="A9">
         <f>IF(B9&lt;&gt;"",COUNTA($B$2:B9),"")</f>
-        <v/>
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:4">

--- a/words.xlsx
+++ b/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8001E1-8BB4-438D-A063-CA3BA2112008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3AC2EE-F08C-40E0-9CDF-F09FA45A17CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5025" yWindow="2430" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12825" yWindow="3165" windowWidth="15105" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="単語" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t>番号</t>
     <rPh sb="0" eb="2">
@@ -143,6 +143,21 @@
   </si>
   <si>
     <t>適合性</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>as present</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在のところ</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Idm</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -610,9 +625,18 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" t="str">
+      <c r="A10">
         <f>IF(B10&lt;&gt;"",COUNTA($B$2:B10),"")</f>
-        <v/>
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:4">

--- a/words.xlsx
+++ b/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3AC2EE-F08C-40E0-9CDF-F09FA45A17CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8012F08-1BD2-472F-A54A-74DE81C9D415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12825" yWindow="3165" windowWidth="15105" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="975" windowWidth="14640" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="単語" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
   <si>
     <t>番号</t>
     <rPh sb="0" eb="2">
@@ -158,6 +158,17 @@
   </si>
   <si>
     <t>Idm</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>merchant</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小売業者</t>
+    <rPh sb="0" eb="4">
+      <t>コウリギョウシャ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -640,9 +651,18 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" t="str">
+      <c r="A11">
         <f>IF(B11&lt;&gt;"",COUNTA($B$2:B11),"")</f>
-        <v/>
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:4">

--- a/words.xlsx
+++ b/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8012F08-1BD2-472F-A54A-74DE81C9D415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F5736F-5695-4771-BB66-4FE4C2900AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="975" windowWidth="14640" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="975" windowWidth="14640" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="単語" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>番号</t>
     <rPh sb="0" eb="2">
@@ -168,6 +168,28 @@
     <t>小売業者</t>
     <rPh sb="0" eb="4">
       <t>コウリギョウシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>be entitled to</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>を持つ◆がある</t>
+    <rPh sb="1" eb="2">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>premises</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敷居</t>
+    <rPh sb="0" eb="2">
+      <t>シキイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -666,15 +688,33 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" t="str">
+      <c r="A12">
         <f>IF(B12&lt;&gt;"",COUNTA($B$2:B12),"")</f>
-        <v/>
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" t="str">
+      <c r="A13">
         <f>IF(B13&lt;&gt;"",COUNTA($B$2:B13),"")</f>
-        <v/>
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:4">

--- a/words.xlsx
+++ b/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F5736F-5695-4771-BB66-4FE4C2900AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F3471A-BE57-4A0A-9C31-77C8074294BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="975" windowWidth="14640" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11025" yWindow="2745" windowWidth="15450" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="単語" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
   <si>
     <t>番号</t>
     <rPh sb="0" eb="2">
@@ -190,6 +190,54 @@
     <t>敷居</t>
     <rPh sb="0" eb="2">
       <t>シキイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>meticulous</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>綿密な</t>
+    <rPh sb="0" eb="2">
+      <t>メンミツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mulfunction</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>故障</t>
+    <rPh sb="0" eb="2">
+      <t>コショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>substantial</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相当な</t>
+    <rPh sb="0" eb="2">
+      <t>ソウトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>live up to～</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>idm</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>～に沿う</t>
+    <rPh sb="2" eb="3">
+      <t>ソ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -718,114 +766,150 @@
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" t="str">
+      <c r="A14">
         <f>IF(B14&lt;&gt;"",COUNTA($B$2:B14),"")</f>
-        <v/>
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" t="str">
+      <c r="A15">
         <f>IF(B15&lt;&gt;"",COUNTA($B$2:B15),"")</f>
-        <v/>
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" t="str">
+      <c r="A16">
         <f>IF(B16&lt;&gt;"",COUNTA($B$2:B16),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="str">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17">
         <f>IF(B17&lt;&gt;"",COUNTA($B$2:B17),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="str">
         <f>IF(B18&lt;&gt;"",COUNTA($B$2:B18),"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:4">
       <c r="A19" t="str">
         <f>IF(B19&lt;&gt;"",COUNTA($B$2:B19),"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:4">
       <c r="A20" t="str">
         <f>IF(B20&lt;&gt;"",COUNTA($B$2:B20),"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:4">
       <c r="A21" t="str">
         <f>IF(B21&lt;&gt;"",COUNTA($B$2:B21),"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:4">
       <c r="A22" t="str">
         <f>IF(B22&lt;&gt;"",COUNTA($B$2:B22),"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:4">
       <c r="A23" t="str">
         <f>IF(B23&lt;&gt;"",COUNTA($B$2:B23),"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:4">
       <c r="A24" t="str">
         <f>IF(B24&lt;&gt;"",COUNTA($B$2:B24),"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:4">
       <c r="A25" t="str">
         <f>IF(B25&lt;&gt;"",COUNTA($B$2:B25),"")</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:4">
       <c r="A26" t="str">
         <f>IF(B26&lt;&gt;"",COUNTA($B$2:B26),"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:4">
       <c r="A27" t="str">
         <f>IF(B27&lt;&gt;"",COUNTA($B$2:B27),"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:4">
       <c r="A28" t="str">
         <f>IF(B28&lt;&gt;"",COUNTA($B$2:B28),"")</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:4">
       <c r="A29" t="str">
         <f>IF(B29&lt;&gt;"",COUNTA($B$2:B29),"")</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:4">
       <c r="A30" t="str">
         <f>IF(B30&lt;&gt;"",COUNTA($B$2:B30),"")</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:4">
       <c r="A31" t="str">
         <f>IF(B31&lt;&gt;"",COUNTA($B$2:B31),"")</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:4">
       <c r="A32" t="str">
         <f>IF(B32&lt;&gt;"",COUNTA($B$2:B32),"")</f>
         <v/>

--- a/words.xlsx
+++ b/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F3471A-BE57-4A0A-9C31-77C8074294BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281F087B-B3E5-4E58-994A-3C2D9900DCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11025" yWindow="2745" windowWidth="15450" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="405" yWindow="0" windowWidth="15450" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="単語" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
   <si>
     <t>番号</t>
     <rPh sb="0" eb="2">
@@ -176,13 +176,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>を持つ◆がある</t>
-    <rPh sb="1" eb="2">
-      <t>モ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>premises</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -238,6 +231,27 @@
     <t>～に沿う</t>
     <rPh sb="2" eb="3">
       <t>ソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>patio</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中庭</t>
+    <rPh sb="0" eb="2">
+      <t>ナカニワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>を持つ資格がある</t>
+    <rPh sb="1" eb="2">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シカク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -747,7 +761,7 @@
         <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -756,13 +770,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
         <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -771,13 +785,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -786,13 +800,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -801,13 +815,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -816,19 +830,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
         <v>38</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>39</v>
       </c>
-      <c r="D17" t="s">
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18">
+        <f>IF(B18&lt;&gt;"",COUNTA($B$2:B18),"")</f>
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="str">
-        <f>IF(B18&lt;&gt;"",COUNTA($B$2:B18),"")</f>
-        <v/>
+      <c r="C18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:4">

--- a/words.xlsx
+++ b/words.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281F087B-B3E5-4E58-994A-3C2D9900DCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A74F53AB-7E52-4022-BB8F-1FCD7FE7A003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="0" windowWidth="15450" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="795" windowWidth="13395" windowHeight="13515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="単語" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="44">
   <si>
     <t>番号</t>
     <rPh sb="0" eb="2">
@@ -253,6 +253,10 @@
     <rPh sb="3" eb="5">
       <t>シカク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>綿密な</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -855,9 +859,18 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" t="str">
+      <c r="A19">
         <f>IF(B19&lt;&gt;"",COUNTA($B$2:B19),"")</f>
-        <v/>
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:4">

--- a/words.xlsx
+++ b/words.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A74F53AB-7E52-4022-BB8F-1FCD7FE7A003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="795" windowWidth="13395" windowHeight="13515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14370" yWindow="1560" windowWidth="13395" windowHeight="13515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="単語" sheetId="1" r:id="rId1"/>

--- a/words.xlsx
+++ b/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A74F53AB-7E52-4022-BB8F-1FCD7FE7A003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285919CE-4B38-402A-925D-F730018827FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14370" yWindow="1560" windowWidth="13395" windowHeight="13515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2685" windowWidth="13395" windowHeight="13515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="単語" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="45">
   <si>
     <t>番号</t>
     <rPh sb="0" eb="2">
@@ -257,6 +257,13 @@
   </si>
   <si>
     <t>綿密な</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テラス、中庭</t>
+    <rPh sb="4" eb="6">
+      <t>ナカニワ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -874,9 +881,18 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" t="str">
+      <c r="A20">
         <f>IF(B20&lt;&gt;"",COUNTA($B$2:B20),"")</f>
-        <v/>
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:4">

--- a/words.xlsx
+++ b/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285919CE-4B38-402A-925D-F730018827FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579967C0-E36A-4FAC-AC01-A33788A7D9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2685" windowWidth="13395" windowHeight="13515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="855" windowWidth="15840" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="単語" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="49">
   <si>
     <t>番号</t>
     <rPh sb="0" eb="2">
@@ -264,6 +264,22 @@
     <rPh sb="4" eb="6">
       <t>ナカニワ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>be about to</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しようとしている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cease to</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やめる</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -896,15 +912,33 @@
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" t="str">
+      <c r="A21">
         <f>IF(B21&lt;&gt;"",COUNTA($B$2:B21),"")</f>
-        <v/>
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" t="str">
+      <c r="A22">
         <f>IF(B22&lt;&gt;"",COUNTA($B$2:B22),"")</f>
-        <v/>
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:4">

--- a/words.xlsx
+++ b/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579967C0-E36A-4FAC-AC01-A33788A7D9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414414D0-45F3-4C56-B65D-E3D23B2E3BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="855" windowWidth="15840" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="45" windowWidth="15840" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="単語" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
   <si>
     <t>番号</t>
     <rPh sb="0" eb="2">
@@ -280,6 +280,25 @@
   </si>
   <si>
     <t>やめる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>utmost</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大限の</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>acknowledge</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>認知する</t>
+    <rPh sb="0" eb="2">
+      <t>ニンチ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -942,15 +961,33 @@
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" t="str">
+      <c r="A23">
         <f>IF(B23&lt;&gt;"",COUNTA($B$2:B23),"")</f>
-        <v/>
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" t="str">
+      <c r="A24">
         <f>IF(B24&lt;&gt;"",COUNTA($B$2:B24),"")</f>
-        <v/>
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:4">
